--- a/Assignments_Status.xlsx
+++ b/Assignments_Status.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="36">
   <si>
     <t>Windows</t>
   </si>
@@ -208,11 +208,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -535,40 +538,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -577,7 +580,7 @@
       <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -586,7 +589,9 @@
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
@@ -597,14 +602,18 @@
       <c r="B4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
@@ -615,14 +624,18 @@
       <c r="B5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
@@ -633,14 +646,18 @@
       <c r="B6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
@@ -651,14 +668,18 @@
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
@@ -669,14 +690,18 @@
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
@@ -687,14 +712,18 @@
       <c r="B9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
@@ -705,14 +734,18 @@
       <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
@@ -723,14 +756,18 @@
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
@@ -741,7 +778,9 @@
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
@@ -759,7 +798,9 @@
       <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D13" s="2" t="s">
         <v>33</v>
       </c>
@@ -777,7 +818,9 @@
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
@@ -795,7 +838,9 @@
       <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D15" s="2" t="s">
         <v>33</v>
       </c>
@@ -813,7 +858,9 @@
       <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D16" s="2" t="s">
         <v>33</v>
       </c>
@@ -831,7 +878,9 @@
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D17" s="2" t="s">
         <v>33</v>
       </c>
@@ -849,7 +898,9 @@
       <c r="B18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D18" s="2" t="s">
         <v>33</v>
       </c>
@@ -867,7 +918,9 @@
       <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D19" s="2" t="s">
         <v>33</v>
       </c>
@@ -901,7 +954,9 @@
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D21" s="2" t="s">
         <v>33</v>
       </c>
@@ -919,7 +974,9 @@
       <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="1"/>
+      <c r="C22" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D22" s="2" t="s">
         <v>33</v>
       </c>
@@ -956,8 +1013,12 @@
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="1"/>
+      <c r="B25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
       <c r="F25" s="1"/>
